--- a/data/trans_bre/P5B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 8,13</t>
+          <t>-6,34; 7,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 3,06</t>
+          <t>-4,11; 2,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 7,35</t>
+          <t>-4,64; 6,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 3,1</t>
+          <t>-7,6; 2,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,31; 461,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,63</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-4,29%</t>
+          <t>-4,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>225,71%</t>
+          <t>227,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,13</t>
+          <t>-1,36; 3,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,52</t>
+          <t>-1,76; 1,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,36</t>
+          <t>0,16; 3,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 25,43</t>
+          <t>-0,13; 27,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,29; 150,07</t>
+          <t>-34,9; 148,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,95; 186,37</t>
+          <t>-73,85; 173,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 1177,55</t>
+          <t>-12,62; 1143,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,03; —</t>
+          <t>-33,25; —</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,47</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,25</t>
+          <t>-2,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>221,82%</t>
+          <t>220,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-84,67%</t>
+          <t>-84,73%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 3,72</t>
+          <t>-2,55; 3,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 6,52</t>
+          <t>-0,41; 6,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -0,46</t>
+          <t>-5,26; -0,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -0,4</t>
+          <t>-5,16; -0,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-81,19; 509,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-75,75; —</t>
+          <t>-75,57; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 153,92</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -937,17 +937,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>268,09%</t>
+          <t>267,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,88</t>
+          <t>-0,86; 2,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,69</t>
+          <t>-0,84; 1,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,83</t>
+          <t>-0,44; 1,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 18,0</t>
+          <t>-0,88; 15,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 132,85</t>
+          <t>-24,23; 123,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 158,5</t>
+          <t>-43,07; 200,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 289,72</t>
+          <t>-27,02; 274,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,2; 1905,86</t>
+          <t>-64,93; 2626,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Estudios-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 7,92</t>
+          <t>-6,1; 8,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 2,87</t>
+          <t>-4,28; 2,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 6,44</t>
+          <t>-4,2; 6,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,77</t>
+          <t>-7,7; 2,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-84,31; 461,94</t>
+          <t>-75,06; 554,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,3</t>
+          <t>-1,26; 3,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,49</t>
+          <t>-1,56; 1,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,14</t>
+          <t>0,36; 3,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 27,45</t>
+          <t>-0,04; 23,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 148,82</t>
+          <t>-35,96; 147,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,85; 173,43</t>
+          <t>-67,46; 224,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 1143,31</t>
+          <t>2,39; 1237,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,25; —</t>
+          <t>-32,76; —</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,75</t>
+          <t>-2,5; 3,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 6,23</t>
+          <t>-0,31; 6,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -0,46</t>
+          <t>-4,45; -0,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; -0,21</t>
+          <t>-5,23; -0,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,27; 582,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-75,57; —</t>
+          <t>-75,43; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,8</t>
+          <t>-0,91; 2,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,86</t>
+          <t>-0,95; 1,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,83</t>
+          <t>-0,41; 1,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 15,06</t>
+          <t>-0,94; 17,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 123,67</t>
+          <t>-25,29; 118,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 200,01</t>
+          <t>-45,73; 217,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 274,41</t>
+          <t>-29,29; 319,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,93; 2626,39</t>
+          <t>-64,12; 3079,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P5B_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P5B_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,03</t>
+          <t>-1,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-57,14%</t>
+          <t>-47,78%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 8,31</t>
+          <t>-5,82; 8,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 2,63</t>
+          <t>-4,2; 3,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 6,55</t>
+          <t>-3,78; 7,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 2,85</t>
+          <t>-6,91; 4,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,06; 554,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,96</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1157,3%</t>
+          <t>167,19%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,16</t>
+          <t>-1,42; 3,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,65</t>
+          <t>-1,68; 1,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,23</t>
+          <t>0,29; 3,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 23,83</t>
+          <t>-0,18; 3,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 147,58</t>
+          <t>-39,29; 150,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,46; 224,56</t>
+          <t>-69,58; 196,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 1237,8</t>
+          <t>-1,12; 1157,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,76; —</t>
+          <t>-55,79; 1738,83</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,28</t>
+          <t>-2,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-84,73%</t>
+          <t>-85,76%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,74</t>
+          <t>-2,48; 3,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 6,0</t>
+          <t>-0,26; 6,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; -0,46</t>
+          <t>-4,59; -0,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,47</t>
+          <t>-6,08; -0,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,27; 582,59</t>
+          <t>-81,19; 509,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-75,43; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>267,72%</t>
+          <t>-12,96%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,8</t>
+          <t>-0,96; 2,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,84</t>
+          <t>-0,84; 1,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,97</t>
+          <t>-0,49; 1,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 17,09</t>
+          <t>-1,24; 1,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 118,67</t>
+          <t>-24,52; 132,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,73; 217,33</t>
+          <t>-43,94; 193,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 319,89</t>
+          <t>-36,16; 275,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 3079,81</t>
+          <t>-71,1; 190,14</t>
         </is>
       </c>
     </row>
